--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 22,10,26 бррсч пок зпф.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ ЗПФ/дв 22,10,26 бррсч пок зпф.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15783E61-A129-4D49-8985-F5B79AA3FEA8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873B577A-9231-4296-B650-1CE4C5F29332}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="192">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -605,6 +605,9 @@
   <si>
     <t>100шт списано (16,10,26)</t>
   </si>
+  <si>
+    <t>26,10,</t>
+  </si>
 </sst>
 </file>
 
@@ -1359,7 +1362,9 @@
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
       <c r="AG4" s="7"/>
-      <c r="AH4" s="9"/>
+      <c r="AH4" s="9" t="s">
+        <v>191</v>
+      </c>
       <c r="AI4" s="5"/>
       <c r="AJ4" s="5"/>
       <c r="AK4" s="5"/>
@@ -2651,7 +2656,7 @@
         <v>45.6</v>
       </c>
       <c r="Q16" s="4">
-        <f t="shared" ref="Q15:Q16" si="6">14*P16-O16-F16</f>
+        <f t="shared" ref="Q16" si="6">14*P16-O16-F16</f>
         <v>178.39999999999998</v>
       </c>
       <c r="R16" s="4">
@@ -2879,7 +2884,7 @@
         <v>38.6</v>
       </c>
       <c r="Q18" s="4">
-        <f t="shared" ref="Q18:Q19" si="7">14*P18-O18-F18</f>
+        <f t="shared" ref="Q18" si="7">14*P18-O18-F18</f>
         <v>292.39999999999998</v>
       </c>
       <c r="R18" s="4">
@@ -3334,7 +3339,7 @@
         <v>62</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" ref="Q22:Q24" si="8">14*P22-O22-F22</f>
+        <f t="shared" ref="Q22" si="8">14*P22-O22-F22</f>
         <v>700</v>
       </c>
       <c r="R22" s="4">
@@ -4201,7 +4206,7 @@
         <v>7.4</v>
       </c>
       <c r="Q29" s="4">
-        <f t="shared" ref="Q26:Q33" si="14">14*P29-O29-F29</f>
+        <f t="shared" ref="Q29" si="14">14*P29-O29-F29</f>
         <v>81.400000000000006</v>
       </c>
       <c r="R29" s="4">
@@ -4924,7 +4929,7 @@
         <v>22.8</v>
       </c>
       <c r="Q35" s="4">
-        <f t="shared" ref="Q35:Q42" si="15">14*P35-O35-F35</f>
+        <f t="shared" ref="Q35:Q36" si="15">14*P35-O35-F35</f>
         <v>145.19999999999999</v>
       </c>
       <c r="R35" s="4">
@@ -6156,7 +6161,7 @@
         <v>23.4</v>
       </c>
       <c r="Q45" s="4">
-        <f t="shared" ref="Q44:Q61" si="25">14*P45-O45-F45</f>
+        <f t="shared" ref="Q45:Q57" si="25">14*P45-O45-F45</f>
         <v>144.59999999999997</v>
       </c>
       <c r="R45" s="4">
@@ -9115,7 +9120,7 @@
         <v>3</v>
       </c>
       <c r="L70" s="5">
-        <f t="shared" ref="L70:L101" si="26">E70-K70</f>
+        <f t="shared" ref="L70:L82" si="26">E70-K70</f>
         <v>76</v>
       </c>
       <c r="M70" s="5"/>
@@ -9133,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="S70" s="5">
-        <f t="shared" ref="S70:S101" si="28">(F70+O70+R70)/P70</f>
+        <f t="shared" ref="S70:S82" si="28">(F70+O70+R70)/P70</f>
         <v>14.177215189873417</v>
       </c>
       <c r="T70" s="5">
@@ -9478,7 +9483,7 @@
         <v>59.8</v>
       </c>
       <c r="Q73" s="4">
-        <f t="shared" ref="Q72:Q82" si="35">14*P73-O73-F73</f>
+        <f t="shared" ref="Q73:Q77" si="35">14*P73-O73-F73</f>
         <v>330.19999999999993</v>
       </c>
       <c r="R73" s="4">
